--- a/backend/outputs/output_basicat/LOG/prod/LOG_prod-FR.xlsx
+++ b/backend/outputs/output_basicat/LOG/prod/LOG_prod-FR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,16 @@
           <t>10.20.0.33</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-023</t>
@@ -767,6 +777,16 @@
           <t>10.20.0.57</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>API-REST-GRC</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-047</t>
@@ -834,6 +854,16 @@
           <t>10.20.1.69</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-059</t>
@@ -901,6 +931,16 @@
           <t>10.20.1.81</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-071</t>
@@ -968,6 +1008,16 @@
           <t>10.20.1.99</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-089</t>
@@ -1035,6 +1085,16 @@
           <t>10.20.1.111</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-101</t>
@@ -1102,6 +1162,16 @@
           <t>10.20.1.123</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-113</t>
@@ -1169,6 +1239,16 @@
           <t>10.20.1.135</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-125</t>
@@ -1236,6 +1316,16 @@
           <t>10.20.1.147</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>API-REST-CRM</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>SGIC-LOGIS-PROD-137</t>
@@ -1252,274 +1342,6 @@
         </is>
       </c>
       <c r="O12" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>oplogis149</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>oplogis149</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>outbound</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ALLOW</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>10.20.0.24</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10.20.1.159</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-149</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>SG-PP-OPS-HTTP</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>oplogis167</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>oplogis167</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>outbound</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ALLOW</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>10.20.0.24</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10.20.1.177</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-167</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>SG-PP-OPS-HTTP</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>oplogis179</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>oplogis179</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>outbound</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALLOW</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>10.20.0.24</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10.20.1.189</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-179</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>SG-PP-OPS-HTTP</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>oplogis191</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>oplogis191</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>outbound</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ALLOW</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>10.20.0.24</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10.20.1.201</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-191</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>SG-PP-OPS-HTTP</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>10009</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
         <is>
           <t>10012</t>
         </is>

--- a/backend/outputs/output_basicat/LOG/prod/LOG_prod-FR.xlsx
+++ b/backend/outputs/output_basicat/LOG/prod/LOG_prod-FR.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10.2.1.8</t>
+          <t>10.20.1.80</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -573,12 +573,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SG_WEB</t>
+          <t>SG-PP-GRC-POSTGRES</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>10009</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10008</t>
         </is>
       </c>
     </row>
@@ -610,7 +615,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -620,7 +625,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10.5.1.20</t>
+          <t>10.20.1.164</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -635,7 +640,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>API-REST-CRM</t>
+          <t>VM2VM-LOG-CRM</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -645,12 +650,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>SG_LOG</t>
+          <t>SG-RC-CRM-VM2VM</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>10009</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>10002</t>
         </is>
       </c>
     </row>
